--- a/结果/试卷整体分析报告.xlsx
+++ b/结果/试卷整体分析报告.xlsx
@@ -439,12 +439,12 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>区分度(与总分相关)</t>
+          <t>题目平均区分度</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>题目平均区分度</t>
+          <t>区分度</t>
         </is>
       </c>
     </row>
@@ -464,11 +464,9 @@
         <v>0.717</v>
       </c>
       <c r="E2" t="n">
-        <v>1</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.399</v>
-      </c>
+        <v>0.348</v>
+      </c>
+      <c r="F2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -485,10 +483,10 @@
       <c r="D3" t="n">
         <v>0.713</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.898</v>
-      </c>
-      <c r="F3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="n">
+        <v>0.372</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -505,10 +503,10 @@
       <c r="D4" t="n">
         <v>0.72</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.887</v>
-      </c>
-      <c r="F4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="n">
+        <v>0.238</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
